--- a/sample-data/ukazkovy-export.xlsx
+++ b/sample-data/ukazkovy-export.xlsx
@@ -206,7 +206,7 @@
     <t>2026</t>
   </si>
   <si>
-    <t>7. 6. 2026 23:14:25</t>
+    <t>12. 6. 2026 13:21:15</t>
   </si>
   <si>
     <t>Značka</t>
@@ -899,7 +899,7 @@
         <v>44</v>
       </c>
       <c r="M6" s="5">
-        <f>SUM(M2:M4)</f>
+        <f>SUM(M2:M5)</f>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1017,7 @@
         <v>44</v>
       </c>
       <c r="G4" s="5">
-        <f>SUM(G2:G2)</f>
+        <f>SUM(G2:G3)</f>
       </c>
     </row>
   </sheetData>
